--- a/data/dividends_info_20260312.xlsx
+++ b/data/dividends_info_20260312.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>51.40000152587891</v>
+        <v>50.65000152587891</v>
       </c>
       <c r="I2" t="n">
-        <v>1.361867663851262</v>
+        <v>1.3820335220372</v>
       </c>
       <c r="J2" t="n">
         <v>347</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>22.64999961853027</v>
+        <v>22.29999923706055</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8609271668175563</v>
+        <v>0.8744394918001969</v>
       </c>
       <c r="J4" t="n">
         <v>102</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>21.64999961853027</v>
+        <v>21.40999984741211</v>
       </c>
       <c r="I5" t="n">
-        <v>3.926097066867768</v>
+        <v>3.970107454730982</v>
       </c>
       <c r="J5" t="n">
         <v>102</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>6.400000095367432</v>
+        <v>6.467999935150146</v>
       </c>
       <c r="I6" t="n">
-        <v>2.832812457787805</v>
+        <v>2.803030331134215</v>
       </c>
       <c r="J6" t="n">
         <v>102</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>10.61999988555908</v>
+        <v>10.39500045776367</v>
       </c>
       <c r="I7" t="n">
-        <v>2.730696827919346</v>
+        <v>2.789802666948503</v>
       </c>
       <c r="J7" t="n">
         <v>67</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>33.18999862670898</v>
+        <v>32.63999938964844</v>
       </c>
       <c r="I8" t="n">
-        <v>6.025911668434178</v>
+        <v>6.127451094972407</v>
       </c>
       <c r="J8" t="n">
         <v>67</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3.930000066757202</v>
+        <v>3.917999982833862</v>
       </c>
       <c r="I9" t="n">
-        <v>2.544529218863702</v>
+        <v>2.552322624760981</v>
       </c>
       <c r="J9" t="n">
         <v>67</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>51.40000152587891</v>
+        <v>50.65000152587891</v>
       </c>
       <c r="I11" t="n">
-        <v>4.280155514961109</v>
+        <v>4.34353392640263</v>
       </c>
       <c r="J11" t="n">
         <v>67</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>7.484000205993652</v>
+        <v>7.159999847412109</v>
       </c>
       <c r="I12" t="n">
-        <v>11.49118087024181</v>
+        <v>12.01117344032956</v>
       </c>
       <c r="J12" t="n">
         <v>67</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1.825000047683716</v>
+        <v>1.809999942779541</v>
       </c>
       <c r="I13" t="n">
-        <v>2.191780764650821</v>
+        <v>2.209944821245335</v>
       </c>
       <c r="J13" t="n">
         <v>67</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>19.41500091552734</v>
+        <v>19.08499908447266</v>
       </c>
       <c r="I14" t="n">
-        <v>4.069018608019686</v>
+        <v>4.139376672240635</v>
       </c>
       <c r="J14" t="n">
         <v>67</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5.321000099182129</v>
+        <v>5.215000152587891</v>
       </c>
       <c r="I15" t="n">
-        <v>3.570757309874965</v>
+        <v>3.643336422640648</v>
       </c>
       <c r="J15" t="n">
         <v>67</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>10.25</v>
+        <v>10.14999961853027</v>
       </c>
       <c r="I16" t="n">
-        <v>4.214634146341464</v>
+        <v>4.256157795428113</v>
       </c>
       <c r="J16" t="n">
         <v>67</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>24.57999992370605</v>
+        <v>24.65999984741211</v>
       </c>
       <c r="I17" t="n">
-        <v>1.790073235824725</v>
+        <v>1.784266028883106</v>
       </c>
       <c r="J17" t="n">
         <v>67</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>53.7400016784668</v>
+        <v>52.93999862670898</v>
       </c>
       <c r="I18" t="n">
-        <v>2.605135757859436</v>
+        <v>2.644503279782255</v>
       </c>
       <c r="J18" t="n">
         <v>67</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>3.019999980926514</v>
+        <v>2.956000089645386</v>
       </c>
       <c r="I19" t="n">
-        <v>9.933774897176066</v>
+        <v>10.14884948924306</v>
       </c>
       <c r="J19" t="n">
         <v>67</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>3.365999937057495</v>
+        <v>3.288000106811523</v>
       </c>
       <c r="I20" t="n">
-        <v>5.050505144946953</v>
+        <v>5.170316133744118</v>
       </c>
       <c r="J20" t="n">
         <v>67</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>4.869999885559082</v>
+        <v>4.889999866485596</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8213552554407904</v>
+        <v>0.8179959323546503</v>
       </c>
       <c r="J21" t="n">
         <v>67</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>30.64999961853027</v>
+        <v>29.89999961853027</v>
       </c>
       <c r="I22" t="n">
-        <v>3.425774920288073</v>
+        <v>3.51170573042172</v>
       </c>
       <c r="J22" t="n">
         <v>67</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>23.31999969482422</v>
+        <v>23.20000076293945</v>
       </c>
       <c r="I23" t="n">
-        <v>2.57289883298398</v>
+        <v>2.586206811503482</v>
       </c>
       <c r="J23" t="n">
         <v>67</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>8.560000419616699</v>
+        <v>8.520000457763672</v>
       </c>
       <c r="I24" t="n">
-        <v>5.963784754380411</v>
+        <v>5.991783715631348</v>
       </c>
       <c r="J24" t="n">
         <v>53</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>18.60000038146973</v>
+        <v>18.70000076293945</v>
       </c>
       <c r="I25" t="n">
-        <v>4.032257981818046</v>
+        <v>4.010695023533825</v>
       </c>
       <c r="J25" t="n">
         <v>53</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>3.950000047683716</v>
+        <v>3.954999923706055</v>
       </c>
       <c r="I26" t="n">
-        <v>3.797468308588</v>
+        <v>3.792667582644139</v>
       </c>
       <c r="J26" t="n">
         <v>53</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>11.5600004196167</v>
+        <v>11.72000026702881</v>
       </c>
       <c r="I27" t="n">
-        <v>1.705614124939086</v>
+        <v>1.682329313205598</v>
       </c>
       <c r="J27" t="n">
         <v>53</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>25.29999923706055</v>
+        <v>25.54999923706055</v>
       </c>
       <c r="I28" t="n">
-        <v>4.347826218068307</v>
+        <v>4.305283885897102</v>
       </c>
       <c r="J28" t="n">
         <v>53</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>26.89999961853027</v>
+        <v>27.85000038146973</v>
       </c>
       <c r="I30" t="n">
-        <v>1.115241651503008</v>
+        <v>1.077199267112427</v>
       </c>
       <c r="J30" t="n">
         <v>53</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>6.179999828338623</v>
+        <v>5.980000019073486</v>
       </c>
       <c r="I31" t="n">
-        <v>2.588996835668408</v>
+        <v>2.675585275747034</v>
       </c>
       <c r="J31" t="n">
         <v>46</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>2.269999980926514</v>
+        <v>2.230000019073486</v>
       </c>
       <c r="I32" t="n">
-        <v>2.863436147407802</v>
+        <v>2.914798181347371</v>
       </c>
       <c r="J32" t="n">
         <v>46</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>6.605000019073486</v>
+        <v>6.644999980926514</v>
       </c>
       <c r="I33" t="n">
-        <v>7.570022688207914</v>
+        <v>7.524454498648243</v>
       </c>
       <c r="J33" t="n">
         <v>39</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>11.76500034332275</v>
+        <v>11.41499996185303</v>
       </c>
       <c r="I34" t="n">
-        <v>4.589885118928008</v>
+        <v>4.7306176242189</v>
       </c>
       <c r="J34" t="n">
         <v>39</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>6.328000068664551</v>
+        <v>6.165999889373779</v>
       </c>
       <c r="I35" t="n">
-        <v>1.580278111803242</v>
+        <v>1.621796980118922</v>
       </c>
       <c r="J35" t="n">
         <v>39</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>294.6000061035156</v>
+        <v>292.6000061035156</v>
       </c>
       <c r="I36" t="n">
-        <v>1.227087550951975</v>
+        <v>1.235475025493024</v>
       </c>
       <c r="J36" t="n">
         <v>39</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>26.79999923706055</v>
+        <v>26.70000076293945</v>
       </c>
       <c r="I37" t="n">
-        <v>5.074627010135566</v>
+        <v>5.09363281325343</v>
       </c>
       <c r="J37" t="n">
         <v>39</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>13.8100004196167</v>
+        <v>13.32999992370605</v>
       </c>
       <c r="I38" t="n">
-        <v>4.236060696776118</v>
+        <v>4.388597174405356</v>
       </c>
       <c r="J38" t="n">
         <v>39</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>16.5049991607666</v>
+        <v>15.86499977111816</v>
       </c>
       <c r="I39" t="n">
-        <v>3.817025337980924</v>
+        <v>3.971005414994706</v>
       </c>
       <c r="J39" t="n">
         <v>39</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>101.1999969482422</v>
+        <v>101.5500030517578</v>
       </c>
       <c r="I40" t="n">
-        <v>0.8893280900594264</v>
+        <v>0.8862628980338776</v>
       </c>
       <c r="J40" t="n">
         <v>39</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>67.59999847412109</v>
+        <v>65.06999969482422</v>
       </c>
       <c r="I41" t="n">
-        <v>2.545562187636385</v>
+        <v>2.644536665238183</v>
       </c>
       <c r="J41" t="n">
         <v>39</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>24.29999923706055</v>
+        <v>22.79999923706055</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5761317053314243</v>
+        <v>0.6140351082662987</v>
       </c>
       <c r="J42" t="n">
         <v>32</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1.480000019073486</v>
+        <v>1.5</v>
       </c>
       <c r="I43" t="n">
-        <v>4.05405400180747</v>
+        <v>4</v>
       </c>
       <c r="J43" t="n">
         <v>32</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1.960000038146973</v>
+        <v>1.940000057220459</v>
       </c>
       <c r="I44" t="n">
-        <v>1.734693843789123</v>
+        <v>1.752577267895219</v>
       </c>
       <c r="J44" t="n">
         <v>18</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>21.28499984741211</v>
+        <v>21.76499938964844</v>
       </c>
       <c r="I45" t="n">
-        <v>1.221517509344082</v>
+        <v>1.194578485141872</v>
       </c>
       <c r="J45" t="n">
         <v>11</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>29.14500045776367</v>
+        <v>28.95999908447266</v>
       </c>
       <c r="I46" t="n">
-        <v>0.3088008186187066</v>
+        <v>0.3107734904876253</v>
       </c>
       <c r="J46" t="n">
         <v>11</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>51.40000152587891</v>
+        <v>50.65000152587891</v>
       </c>
       <c r="I47" t="n">
-        <v>1.2645914021476</v>
+        <v>1.283316841891686</v>
       </c>
       <c r="J47" t="n">
         <v>-17</v>
@@ -4282,7 +4282,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4299,7 +4299,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4316,7 +4316,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4452,7 +4452,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4486,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>NEXT RE SIIQ S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4503,7 +4503,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>NEXT RE SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4554,7 +4554,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4571,7 +4571,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4588,7 +4588,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4605,7 +4605,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4639,7 +4639,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4656,7 +4656,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4673,7 +4673,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4690,7 +4690,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4707,7 +4707,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4724,7 +4724,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4741,7 +4741,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4758,7 +4758,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4775,7 +4775,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4792,7 +4792,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4809,7 +4809,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4826,7 +4826,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Antares Vision S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4843,7 +4843,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4860,7 +4860,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4877,7 +4877,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4887,14 +4887,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4911,7 +4911,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4928,7 +4928,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4945,7 +4945,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4962,7 +4962,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4979,7 +4979,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4989,14 +4989,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>Antares Vision S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5013,7 +5013,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5023,14 +5023,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5040,14 +5040,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Braga Moro Sistemi di Energia S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5064,7 +5064,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5081,7 +5081,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5091,14 +5091,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5115,7 +5115,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5125,14 +5125,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Egomnia S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5142,14 +5142,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5166,7 +5166,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5176,14 +5176,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>Braga Moro Sistemi di Energia S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5200,7 +5200,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5217,7 +5217,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Egomnia S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5234,7 +5234,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5251,7 +5251,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5268,7 +5268,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5285,7 +5285,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5302,7 +5302,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5319,7 +5319,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Allcore S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5329,14 +5329,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5346,14 +5346,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5370,7 +5370,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5387,7 +5387,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5404,7 +5404,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5414,14 +5414,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5431,14 +5431,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5455,7 +5455,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5472,7 +5472,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>rino petino S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5489,7 +5489,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5499,14 +5499,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5523,7 +5523,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5533,14 +5533,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5557,7 +5557,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5567,14 +5567,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5591,7 +5591,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5601,14 +5601,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5625,7 +5625,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5635,14 +5635,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>Confinvest F.L. S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5659,7 +5659,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5669,14 +5669,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5693,7 +5693,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5710,7 +5710,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5720,14 +5720,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5744,7 +5744,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5754,14 +5754,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5795,7 +5795,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5812,7 +5812,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5829,7 +5829,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5846,7 +5846,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5863,7 +5863,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5880,7 +5880,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -5890,14 +5890,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -5914,7 +5914,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -5931,7 +5931,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -5948,7 +5948,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -5965,7 +5965,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -5982,7 +5982,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -5992,14 +5992,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -6009,14 +6009,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -6033,7 +6033,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -6043,14 +6043,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -6067,7 +6067,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -6084,7 +6084,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -6094,14 +6094,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -6111,14 +6111,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -6135,7 +6135,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -6152,7 +6152,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -6169,7 +6169,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -6186,7 +6186,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -6203,7 +6203,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -6220,7 +6220,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6237,7 +6237,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6254,7 +6254,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6271,7 +6271,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ELES S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6288,7 +6288,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6305,7 +6305,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -6322,7 +6322,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -6339,7 +6339,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6356,7 +6356,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6373,7 +6373,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -6390,7 +6390,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6407,7 +6407,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -6417,14 +6417,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -6441,7 +6441,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -6458,7 +6458,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -6475,7 +6475,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -6492,7 +6492,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -6502,14 +6502,14 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -6526,7 +6526,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -6543,7 +6543,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -6553,14 +6553,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -6577,7 +6577,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -6594,7 +6594,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -6611,7 +6611,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -6628,7 +6628,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -6645,7 +6645,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -6662,7 +6662,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -6672,14 +6672,14 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -6696,7 +6696,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -6713,7 +6713,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>ELES S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -6730,7 +6730,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -6747,7 +6747,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -6764,7 +6764,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -6781,7 +6781,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -6798,7 +6798,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -6815,7 +6815,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -6832,7 +6832,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -6849,7 +6849,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -6866,7 +6866,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -6883,7 +6883,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -6893,14 +6893,14 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -6917,7 +6917,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -6934,7 +6934,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -6951,7 +6951,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>HEALTH ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -6968,7 +6968,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -6985,7 +6985,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -7002,7 +7002,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -7019,7 +7019,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -7036,7 +7036,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -7053,7 +7053,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -7070,7 +7070,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -7080,14 +7080,14 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -7104,7 +7104,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -7114,14 +7114,14 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -7131,14 +7131,14 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -7155,7 +7155,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -7172,7 +7172,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -7189,7 +7189,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -7206,7 +7206,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -7223,7 +7223,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -7240,7 +7240,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -7250,14 +7250,14 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -7291,7 +7291,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -7301,14 +7301,14 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -7325,7 +7325,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -7342,7 +7342,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -7359,7 +7359,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>HEALTH ITALIA S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -7376,7 +7376,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -7393,7 +7393,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -7410,7 +7410,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -7427,7 +7427,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -7444,7 +7444,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -7461,7 +7461,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -7478,7 +7478,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -7495,7 +7495,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -7512,7 +7512,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -7529,7 +7529,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -7546,7 +7546,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -7563,7 +7563,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -7580,7 +7580,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -7590,14 +7590,14 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -7607,14 +7607,14 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -7631,7 +7631,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -7641,14 +7641,14 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -7658,14 +7658,14 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -7682,7 +7682,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -7699,7 +7699,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -7716,7 +7716,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -7733,7 +7733,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -7750,7 +7750,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -7767,7 +7767,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -7784,7 +7784,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -7794,7 +7794,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -7818,7 +7818,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -7828,14 +7828,14 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>NEUROSOFT</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -7852,7 +7852,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -7869,7 +7869,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -7886,7 +7886,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -7903,7 +7903,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -7920,7 +7920,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -7937,7 +7937,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -7954,7 +7954,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -7971,7 +7971,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -7988,7 +7988,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -8005,7 +8005,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -8015,14 +8015,14 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -8032,14 +8032,14 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -8056,7 +8056,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -8066,14 +8066,14 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -8090,7 +8090,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>NEUROSOFT</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -8107,7 +8107,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -8124,7 +8124,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -8134,14 +8134,14 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -8158,7 +8158,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -8168,14 +8168,14 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -8192,7 +8192,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -8209,7 +8209,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -8226,7 +8226,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -8243,7 +8243,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -8253,14 +8253,14 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -8277,7 +8277,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -8287,14 +8287,14 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -8311,7 +8311,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -8328,7 +8328,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -8338,14 +8338,14 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -8355,7 +8355,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -8389,14 +8389,14 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -8406,14 +8406,14 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>I.CO.P. S.p.A. Società Benefit</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -8423,14 +8423,14 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>I.CO.P. S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -8440,7 +8440,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -8481,7 +8481,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -8491,14 +8491,14 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -8559,14 +8559,14 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Masi Agricola S.p.A.</t>
+          <t>RT&amp;L S.P.A.</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -8583,7 +8583,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>RT&amp;L S.P.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -8600,7 +8600,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -8610,14 +8610,14 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Masi Agricola S.p.A.</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -8627,14 +8627,14 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -8676,356 +8676,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IT0005508921</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>7.484000205993652</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>11.49118087024181</v>
-      </c>
-      <c r="I2" t="n">
-        <v>67</v>
-      </c>
-      <c r="J2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Basic Net S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>IT0001033700</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-04-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>6.179999828338623</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>2.588996835668408</v>
-      </c>
-      <c r="I3" t="n">
-        <v>46</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Confinvest F.L. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>IT0005379604</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-03-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>1.960000038146973</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1.734693843789123</v>
-      </c>
-      <c r="I4" t="n">
-        <v>18</v>
-      </c>
-      <c r="J4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>SAIPEM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>IT0005495657</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>3.365999937057495</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>5.050505144946953</v>
-      </c>
-      <c r="I5" t="n">
-        <v>67</v>
-      </c>
-      <c r="J5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>SYS-DAT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>IT0005595423</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>4.869999885559082</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>0.8213552554407904</v>
-      </c>
-      <c r="I6" t="n">
-        <v>67</v>
-      </c>
-      <c r="J6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Toscana Aeroporti S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>IT0000214293</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2026-07-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>18.20000076293945</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.376</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>2.06593397933063</v>
-      </c>
-      <c r="I7" t="n">
-        <v>130</v>
-      </c>
-      <c r="J7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>WIIT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>IT0005440893</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2026-05-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>26.89999961853027</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>1.115241651503008</v>
-      </c>
-      <c r="I8" t="n">
-        <v>53</v>
-      </c>
-      <c r="J8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9036,44 +8689,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Impianti S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>